--- a/recruiter_forms/003_sales_employment_interview_form--recruiter_forms.xlsx
+++ b/recruiter_forms/003_sales_employment_interview_form--recruiter_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,12 +1102,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales_role_1'}</t>
+          <t>sales_role_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales Role 1'}</t>
+          <t>Sales Role 1</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sales_role_2'}</t>
+          <t>sales_role_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sales Role 2'}</t>
+          <t>Sales Role 2</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sales_role_3'}</t>
+          <t>sales_role_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sales Role 3'}</t>
+          <t>Sales Role 3</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': "Bachelor's degree"}</t>
+          <t>Bachelor's degree</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"master's_degree"}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "Master's degree"}</t>
+          <t>Master's degree</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'PhD'}</t>
+          <t>PhD</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'problem-solving'}</t>
+          <t>problem-solving</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Problem-solving'}</t>
+          <t>Problem-solving</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Personal'}</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'professional'}</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Professional'}</t>
+          <t>Professional</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'health'}</t>
+          <t>health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Health'}</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'vision'}</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Vision'}</t>
+          <t>Vision</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'dental'}</t>
+          <t>dental</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Dental'}</t>
+          <t>Dental</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full time'}</t>
+          <t>Full time</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Part time'}</t>
+          <t>Part time</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'home_office'}</t>
+          <t>home_office</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Home office'}</t>
+          <t>Home office</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'weeks'}</t>
+          <t>weeks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Weeks'}</t>
+          <t>Weeks</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'months'}</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Months'}</t>
+          <t>Months</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'years'}</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Years'}</t>
+          <t>Years</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'weeks'}</t>
+          <t>weeks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'weeks'}</t>
+          <t>weeks</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'months'}</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'months'}</t>
+          <t>months</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'years'}</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'years'}</t>
+          <t>years</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'s'}</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 's'}</t>
+          <t>s</t>
         </is>
       </c>
     </row>
@@ -1662,29 +1662,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'s'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 's'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>termination_notice_notice_period_unit_short_suffix_choices</t>
+          <t>reporting_manager_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'s'}</t>
+          <t>directly_with_a_manager</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 's'}</t>
+          <t>Directly with a manager</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'directly_with_a_manager'}</t>
+          <t>indirectly_with_a_manager</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Directly with a manager'}</t>
+          <t>Indirectly with a manager</t>
         </is>
       </c>
     </row>
@@ -1713,29 +1713,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'indirectly_with_a_manager'}</t>
+          <t>no_manager</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Indirectly with a manager'}</t>
+          <t>No manager</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>reporting_manager_choices</t>
+          <t>supervisor_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'no_manager'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'No manager'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1747,29 +1747,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>supervisor_choices</t>
+          <t>team_management_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1781,29 +1781,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>team_management_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
